--- a/artfynd/A 36252-2022 artfynd.xlsx
+++ b/artfynd/A 36252-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36252-2022 artfynd.xlsx
+++ b/artfynd/A 36252-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651721</v>
+        <v>119651719</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,42 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bågede NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491325</v>
+        <v>491419</v>
       </c>
       <c r="R7" t="n">
-        <v>7136145</v>
+        <v>7136146</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1340,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flertalet</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651722</v>
+        <v>119651718</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,25 +1379,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491280</v>
+        <v>491388</v>
       </c>
       <c r="R8" t="n">
-        <v>7136272</v>
+        <v>7136215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,6 +1443,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651726</v>
+        <v>119651712</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491441</v>
+        <v>491424</v>
       </c>
       <c r="R9" t="n">
-        <v>7136146</v>
+        <v>7136095</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651712</v>
+        <v>119651720</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491424</v>
+        <v>491238</v>
       </c>
       <c r="R10" t="n">
-        <v>7136095</v>
+        <v>7136323</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,6 +1652,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651727</v>
+        <v>119651722</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>91494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1721,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491454</v>
+        <v>491280</v>
       </c>
       <c r="R11" t="n">
-        <v>7136146</v>
+        <v>7136272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651718</v>
+        <v>119651717</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1823,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491388</v>
+        <v>491400</v>
       </c>
       <c r="R12" t="n">
-        <v>7136215</v>
+        <v>7136232</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651719</v>
+        <v>119651721</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,34 +1908,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bågede NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491419</v>
+        <v>491325</v>
       </c>
       <c r="R13" t="n">
-        <v>7136146</v>
+        <v>7136145</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1980,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Flertalet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651717</v>
+        <v>119651726</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,25 +2019,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2037,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491400</v>
+        <v>491441</v>
       </c>
       <c r="R14" t="n">
-        <v>7136232</v>
+        <v>7136146</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,11 +2083,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,10 +2109,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651720</v>
+        <v>119651727</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2116,25 +2121,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2144,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491238</v>
+        <v>491454</v>
       </c>
       <c r="R15" t="n">
-        <v>7136323</v>
+        <v>7136146</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,11 +2185,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 36252-2022 artfynd.xlsx
+++ b/artfynd/A 36252-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651719</v>
+        <v>119651712</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491419</v>
+        <v>491424</v>
       </c>
       <c r="R7" t="n">
-        <v>7136146</v>
+        <v>7136095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,11 +1336,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651718</v>
+        <v>119651721</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1378,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bågede NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491388</v>
+        <v>491325</v>
       </c>
       <c r="R8" t="n">
-        <v>7136215</v>
+        <v>7136145</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1450,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Flertalet</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651712</v>
+        <v>119651717</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491424</v>
+        <v>491400</v>
       </c>
       <c r="R9" t="n">
-        <v>7136095</v>
+        <v>7136232</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,6 +1553,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651722</v>
+        <v>119651726</v>
       </c>
       <c r="B11" t="n">
-        <v>91494</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491280</v>
+        <v>491441</v>
       </c>
       <c r="R11" t="n">
-        <v>7136272</v>
+        <v>7136146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651717</v>
+        <v>119651727</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1805,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491400</v>
+        <v>491454</v>
       </c>
       <c r="R12" t="n">
-        <v>7136232</v>
+        <v>7136146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,11 +1869,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651721</v>
+        <v>119651719</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,42 +1911,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bågede NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491325</v>
+        <v>491419</v>
       </c>
       <c r="R13" t="n">
-        <v>7136145</v>
+        <v>7136146</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1975,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flertalet</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651726</v>
+        <v>119651718</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,25 +2014,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2047,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491441</v>
+        <v>491388</v>
       </c>
       <c r="R14" t="n">
-        <v>7136146</v>
+        <v>7136215</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,6 +2078,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,10 +2109,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651727</v>
+        <v>119651722</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>91494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,25 +2121,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491454</v>
+        <v>491280</v>
       </c>
       <c r="R15" t="n">
-        <v>7136146</v>
+        <v>7136272</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 36252-2022 artfynd.xlsx
+++ b/artfynd/A 36252-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651712</v>
+        <v>119651718</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491424</v>
+        <v>491388</v>
       </c>
       <c r="R7" t="n">
-        <v>7136095</v>
+        <v>7136215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,6 +1336,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651721</v>
+        <v>119651720</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,42 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bågede NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491325</v>
+        <v>491238</v>
       </c>
       <c r="R8" t="n">
-        <v>7136145</v>
+        <v>7136323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1447,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flertalet</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651717</v>
+        <v>119651722</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>91494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491400</v>
+        <v>491280</v>
       </c>
       <c r="R9" t="n">
-        <v>7136232</v>
+        <v>7136272</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,11 +1550,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651720</v>
+        <v>119651721</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,34 +1592,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bågede NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491238</v>
+        <v>491325</v>
       </c>
       <c r="R10" t="n">
-        <v>7136323</v>
+        <v>7136145</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Flertalet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651726</v>
+        <v>119651719</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491441</v>
+        <v>491419</v>
       </c>
       <c r="R11" t="n">
         <v>7136146</v>
@@ -1767,6 +1767,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651727</v>
+        <v>119651717</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,25 +1810,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1833,10 +1838,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491454</v>
+        <v>491400</v>
       </c>
       <c r="R12" t="n">
-        <v>7136146</v>
+        <v>7136232</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,6 +1874,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651719</v>
+        <v>119651712</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,21 +1921,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1935,10 +1945,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491419</v>
+        <v>491424</v>
       </c>
       <c r="R13" t="n">
-        <v>7136146</v>
+        <v>7136095</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,11 +1981,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651718</v>
+        <v>119651727</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2014,25 +2019,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2042,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491388</v>
+        <v>491454</v>
       </c>
       <c r="R14" t="n">
-        <v>7136215</v>
+        <v>7136146</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,11 +2083,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,10 +2109,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651722</v>
+        <v>119651726</v>
       </c>
       <c r="B15" t="n">
-        <v>91494</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,25 +2121,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491280</v>
+        <v>491441</v>
       </c>
       <c r="R15" t="n">
-        <v>7136272</v>
+        <v>7136146</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 36252-2022 artfynd.xlsx
+++ b/artfynd/A 36252-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105315616</v>
+        <v>105315614</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nösterviken, Jmt</t>
+          <t>Lappaltaret, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491331.7698692148</v>
+        <v>491358</v>
       </c>
       <c r="R2" t="n">
-        <v>7136334.891665307</v>
+        <v>7136183</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-05-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105315614</v>
+        <v>105315616</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,14 +808,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lappaltaret, Jmt</t>
+          <t>Nösterviken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491357.8069381543</v>
+        <v>491332</v>
       </c>
       <c r="R3" t="n">
-        <v>7136183.161965849</v>
+        <v>7136335</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +845,9 @@
           <t>2022-05-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105312471</v>
+        <v>119651712</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lappaltaret, Jmt</t>
+          <t>Bågede NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491366.3183645827</v>
+        <v>491424</v>
       </c>
       <c r="R4" t="n">
-        <v>7136278.465691836</v>
+        <v>7136095</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,36 +960,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105312464</v>
+        <v>105890637</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491453.6779609267</v>
+        <v>491352</v>
       </c>
       <c r="R5" t="n">
-        <v>7136334.549817464</v>
+        <v>7136300</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,19 +1044,9 @@
           <t>2022-05-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,53 +1078,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105890637</v>
+        <v>119651722</v>
       </c>
       <c r="B6" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nösterviken, Jmt</t>
+          <t>Bågede NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491352.0625308682</v>
+        <v>491280</v>
       </c>
       <c r="R6" t="n">
-        <v>7136300.170791709</v>
+        <v>7136272</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,22 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,74 +1159,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651718</v>
+        <v>105312464</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bågede NÖ, Jmt</t>
+          <t>Nösterviken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491388</v>
+        <v>491454</v>
       </c>
       <c r="R7" t="n">
-        <v>7136215</v>
+        <v>7136335</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,17 +1240,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,31 +1256,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651720</v>
+        <v>105312471</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,37 +1288,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bågede NÖ, Jmt</t>
+          <t>Lappaltaret, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491238</v>
+        <v>491366</v>
       </c>
       <c r="R8" t="n">
-        <v>7136323</v>
+        <v>7136278</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,17 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,31 +1358,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651722</v>
+        <v>105312465</v>
       </c>
       <c r="B9" t="n">
-        <v>91494</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,37 +1390,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bågede NÖ, Jmt</t>
+          <t>Nösterviken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491280</v>
+        <v>491471</v>
       </c>
       <c r="R9" t="n">
-        <v>7136272</v>
+        <v>7136344</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,12 +1444,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,31 +1460,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651721</v>
+        <v>119651717</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,42 +1492,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bågede NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491325</v>
+        <v>491400</v>
       </c>
       <c r="R10" t="n">
-        <v>7136145</v>
+        <v>7136232</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flertalet</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,15 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651719</v>
+        <v>119651718</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491419</v>
+        <v>491388</v>
       </c>
       <c r="R11" t="n">
-        <v>7136146</v>
+        <v>7136215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1658,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651717</v>
+        <v>119651719</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491400</v>
+        <v>491419</v>
       </c>
       <c r="R12" t="n">
-        <v>7136232</v>
+        <v>7136146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,7 +1760,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,15 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651712</v>
+        <v>119651720</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,21 +1798,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491424</v>
+        <v>491238</v>
       </c>
       <c r="R13" t="n">
-        <v>7136095</v>
+        <v>7136323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,6 +1858,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,50 +1889,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651727</v>
+        <v>119651721</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bågede NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491454</v>
+        <v>491325</v>
       </c>
       <c r="R14" t="n">
-        <v>7136146</v>
+        <v>7136145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,6 +1968,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flertalet</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,12 +2002,7 @@
         <v>119651726</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,6 +2093,103 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>119651727</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bågede NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>491454</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7136146</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36252-2022 artfynd.xlsx
+++ b/artfynd/A 36252-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315614</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315616</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651712</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105890637</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651722</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312464</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312471</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312465</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651717</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651718</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651719</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651720</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651721</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2093,6 +2163,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651726</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2190,8 +2265,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651727</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>